--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_ELK_BULL_ALL.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_ELK_BULL_ALL.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N356"/>
+  <dimension ref="A1:O356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -598,10 +599,15 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -657,7 +663,8 @@
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -713,7 +720,8 @@
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -769,7 +777,8 @@
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -825,7 +834,8 @@
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -881,7 +891,8 @@
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -937,7 +948,8 @@
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
@@ -997,7 +1009,8 @@
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -1053,7 +1066,8 @@
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>8.9</t>
         </is>
@@ -1109,7 +1123,8 @@
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1165,7 +1180,8 @@
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="6" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -1225,7 +1241,8 @@
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>9.9</t>
         </is>
@@ -1292,8 +1309,17 @@
           <t>76.9</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="6" t="inlineStr">
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>12.8</t>
         </is>
@@ -1360,8 +1386,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
@@ -1428,8 +1463,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="6" t="inlineStr">
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -1496,8 +1540,17 @@
           <t>40</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>9.9</t>
         </is>
@@ -1564,8 +1617,17 @@
           <t>30.4</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr">
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>13.9</t>
         </is>
@@ -1632,8 +1694,17 @@
           <t>31.8</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1700,8 +1771,17 @@
           <t>41.5</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr"/>
-      <c r="N21" s="6" t="inlineStr">
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>11.4</t>
         </is>
@@ -1768,8 +1848,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1836,8 +1925,17 @@
           <t>38.1</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="6" t="inlineStr">
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
@@ -1904,8 +2002,17 @@
           <t>37.5</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
@@ -1972,8 +2079,17 @@
           <t>38.9</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="6" t="inlineStr">
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
         <is>
           <t>15.1</t>
         </is>
@@ -2040,8 +2156,17 @@
           <t>33.3</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>13.1</t>
         </is>
@@ -2108,8 +2233,17 @@
           <t>55.2</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr"/>
-      <c r="N27" s="6" t="inlineStr">
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
         <is>
           <t>15.1</t>
         </is>
@@ -2176,8 +2310,17 @@
           <t>28</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>13.1</t>
         </is>
@@ -2244,8 +2387,17 @@
           <t>25.4</t>
         </is>
       </c>
-      <c r="M29" s="6" t="inlineStr"/>
-      <c r="N29" s="6" t="inlineStr">
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
         <is>
           <t>13.4</t>
         </is>
@@ -2312,8 +2464,17 @@
           <t>90.9</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -2380,8 +2541,17 @@
           <t>88.2</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr"/>
-      <c r="N31" s="6" t="inlineStr">
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -2448,8 +2618,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr"/>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2516,8 +2695,17 @@
           <t>75</t>
         </is>
       </c>
-      <c r="M33" s="6" t="inlineStr"/>
-      <c r="N33" s="6" t="inlineStr">
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2584,8 +2772,17 @@
           <t>50</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr"/>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -2652,8 +2849,17 @@
           <t>50</t>
         </is>
       </c>
-      <c r="M35" s="6" t="inlineStr"/>
-      <c r="N35" s="6" t="inlineStr">
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2720,8 +2926,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M36" s="4" t="inlineStr"/>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -2788,8 +3003,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M37" s="6" t="inlineStr"/>
-      <c r="N37" s="6" t="inlineStr">
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -2856,8 +3080,17 @@
           <t>70.8</t>
         </is>
       </c>
-      <c r="M38" s="4" t="inlineStr"/>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -2924,8 +3157,17 @@
           <t>81.1</t>
         </is>
       </c>
-      <c r="M39" s="6" t="inlineStr"/>
-      <c r="N39" s="6" t="inlineStr">
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -2992,8 +3234,17 @@
           <t>68.8</t>
         </is>
       </c>
-      <c r="M40" s="4" t="inlineStr"/>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -3060,8 +3311,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M41" s="6" t="inlineStr"/>
-      <c r="N41" s="6" t="inlineStr">
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O41" s="6" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -3128,8 +3388,17 @@
           <t>85.7</t>
         </is>
       </c>
-      <c r="M42" s="4" t="inlineStr"/>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>12.7</t>
         </is>
@@ -3196,8 +3465,17 @@
           <t>47.1</t>
         </is>
       </c>
-      <c r="M43" s="6" t="inlineStr"/>
-      <c r="N43" s="6" t="inlineStr">
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O43" s="6" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -3264,8 +3542,17 @@
           <t>42.9</t>
         </is>
       </c>
-      <c r="M44" s="4" t="inlineStr"/>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -3332,8 +3619,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M45" s="6" t="inlineStr"/>
-      <c r="N45" s="6" t="inlineStr">
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
@@ -3400,8 +3696,17 @@
           <t>93.3</t>
         </is>
       </c>
-      <c r="M46" s="4" t="inlineStr"/>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -3468,8 +3773,17 @@
           <t>87.5</t>
         </is>
       </c>
-      <c r="M47" s="6" t="inlineStr"/>
-      <c r="N47" s="6" t="inlineStr">
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -3536,8 +3850,17 @@
           <t>93.3</t>
         </is>
       </c>
-      <c r="M48" s="4" t="inlineStr"/>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -3604,8 +3927,17 @@
           <t>90.9</t>
         </is>
       </c>
-      <c r="M49" s="6" t="inlineStr"/>
-      <c r="N49" s="6" t="inlineStr">
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -3672,8 +4004,17 @@
           <t>91.7</t>
         </is>
       </c>
-      <c r="M50" s="4" t="inlineStr"/>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -3740,8 +4081,17 @@
           <t>84.6</t>
         </is>
       </c>
-      <c r="M51" s="6" t="inlineStr"/>
-      <c r="N51" s="6" t="inlineStr">
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O51" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -3808,8 +4158,17 @@
           <t>84.2</t>
         </is>
       </c>
-      <c r="M52" s="4" t="inlineStr"/>
-      <c r="N52" s="4" t="inlineStr">
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -3876,8 +4235,17 @@
           <t>57.9</t>
         </is>
       </c>
-      <c r="M53" s="6" t="inlineStr"/>
-      <c r="N53" s="6" t="inlineStr">
+      <c r="M53" s="6" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
@@ -3944,8 +4312,17 @@
           <t>84.4</t>
         </is>
       </c>
-      <c r="M54" s="4" t="inlineStr"/>
-      <c r="N54" s="4" t="inlineStr">
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -4012,8 +4389,17 @@
           <t>78.9</t>
         </is>
       </c>
-      <c r="M55" s="6" t="inlineStr"/>
-      <c r="N55" s="6" t="inlineStr">
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O55" s="6" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -4080,8 +4466,17 @@
           <t>70</t>
         </is>
       </c>
-      <c r="M56" s="4" t="inlineStr"/>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -4148,8 +4543,17 @@
           <t>81.8</t>
         </is>
       </c>
-      <c r="M57" s="6" t="inlineStr"/>
-      <c r="N57" s="6" t="inlineStr">
+      <c r="M57" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O57" s="6" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -4216,8 +4620,17 @@
           <t>80</t>
         </is>
       </c>
-      <c r="M58" s="4" t="inlineStr"/>
-      <c r="N58" s="4" t="inlineStr">
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O58" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -4284,8 +4697,17 @@
           <t>67.6</t>
         </is>
       </c>
-      <c r="M59" s="6" t="inlineStr"/>
-      <c r="N59" s="6" t="inlineStr">
+      <c r="M59" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O59" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -4352,8 +4774,17 @@
           <t>74</t>
         </is>
       </c>
-      <c r="M60" s="4" t="inlineStr"/>
-      <c r="N60" s="4" t="inlineStr">
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O60" s="4" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -4420,8 +4851,17 @@
           <t>92.9</t>
         </is>
       </c>
-      <c r="M61" s="6" t="inlineStr"/>
-      <c r="N61" s="6" t="inlineStr">
+      <c r="M61" s="6" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="O61" s="6" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -4488,8 +4928,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M62" s="4" t="inlineStr"/>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="O62" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -4556,8 +5005,17 @@
           <t>42.9</t>
         </is>
       </c>
-      <c r="M63" s="6" t="inlineStr"/>
-      <c r="N63" s="6" t="inlineStr">
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O63" s="6" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
@@ -4624,8 +5082,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M64" s="4" t="inlineStr"/>
-      <c r="N64" s="4" t="inlineStr">
+      <c r="M64" s="4" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O64" s="4" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
@@ -4692,8 +5159,17 @@
           <t>72.1</t>
         </is>
       </c>
-      <c r="M65" s="6" t="inlineStr"/>
-      <c r="N65" s="6" t="inlineStr">
+      <c r="M65" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O65" s="6" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -4760,8 +5236,17 @@
           <t>69.2</t>
         </is>
       </c>
-      <c r="M66" s="4" t="inlineStr"/>
-      <c r="N66" s="4" t="inlineStr">
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O66" s="4" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
@@ -4828,8 +5313,17 @@
           <t>58.3</t>
         </is>
       </c>
-      <c r="M67" s="6" t="inlineStr"/>
-      <c r="N67" s="6" t="inlineStr">
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O67" s="6" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -4896,8 +5390,17 @@
           <t>83.3</t>
         </is>
       </c>
-      <c r="M68" s="4" t="inlineStr"/>
-      <c r="N68" s="4" t="inlineStr">
+      <c r="M68" s="4" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O68" s="4" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -4964,8 +5467,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="6" t="inlineStr">
+      <c r="M69" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O69" s="6" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -5032,8 +5544,17 @@
           <t>75</t>
         </is>
       </c>
-      <c r="M70" s="4" t="inlineStr"/>
-      <c r="N70" s="4" t="inlineStr">
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O70" s="4" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -5100,8 +5621,17 @@
           <t>75</t>
         </is>
       </c>
-      <c r="M71" s="6" t="inlineStr"/>
-      <c r="N71" s="6" t="inlineStr">
+      <c r="M71" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O71" s="6" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -5168,8 +5698,17 @@
           <t>76.4</t>
         </is>
       </c>
-      <c r="M72" s="4" t="inlineStr"/>
-      <c r="N72" s="4" t="inlineStr">
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O72" s="4" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -5236,8 +5775,17 @@
           <t>76.5</t>
         </is>
       </c>
-      <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="6" t="inlineStr">
+      <c r="M73" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O73" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -5304,8 +5852,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M74" s="4" t="inlineStr"/>
-      <c r="N74" s="4" t="inlineStr">
+      <c r="M74" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O74" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -5372,8 +5929,17 @@
           <t>65.7</t>
         </is>
       </c>
-      <c r="M75" s="6" t="inlineStr"/>
-      <c r="N75" s="6" t="inlineStr">
+      <c r="M75" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O75" s="6" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -5440,8 +6006,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M76" s="4" t="inlineStr"/>
-      <c r="N76" s="4" t="inlineStr">
+      <c r="M76" s="4" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="O76" s="4" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -5508,8 +6083,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M77" s="6" t="inlineStr"/>
-      <c r="N77" s="6" t="inlineStr">
+      <c r="M77" s="6" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="O77" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5576,8 +6160,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M78" s="4" t="inlineStr"/>
-      <c r="N78" s="4" t="inlineStr">
+      <c r="M78" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O78" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -5644,8 +6237,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M79" s="6" t="inlineStr"/>
-      <c r="N79" s="6" t="inlineStr">
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O79" s="6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -5712,8 +6314,17 @@
           <t>73.9</t>
         </is>
       </c>
-      <c r="M80" s="4" t="inlineStr"/>
-      <c r="N80" s="4" t="inlineStr">
+      <c r="M80" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O80" s="4" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
@@ -5780,8 +6391,17 @@
           <t>50</t>
         </is>
       </c>
-      <c r="M81" s="6" t="inlineStr"/>
-      <c r="N81" s="6" t="inlineStr">
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O81" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -5848,8 +6468,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M82" s="4" t="inlineStr"/>
-      <c r="N82" s="4" t="inlineStr">
+      <c r="M82" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O82" s="4" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
@@ -5916,8 +6545,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M83" s="6" t="inlineStr"/>
-      <c r="N83" s="6" t="inlineStr">
+      <c r="M83" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O83" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -5984,8 +6622,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M84" s="4" t="inlineStr"/>
-      <c r="N84" s="4" t="inlineStr">
+      <c r="M84" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O84" s="4" t="inlineStr">
         <is>
           <t>12.3</t>
         </is>
@@ -6052,8 +6699,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M85" s="6" t="inlineStr"/>
-      <c r="N85" s="6" t="inlineStr">
+      <c r="M85" s="6" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O85" s="6" t="inlineStr">
         <is>
           <t>10.5</t>
         </is>
@@ -6120,8 +6776,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M86" s="4" t="inlineStr"/>
-      <c r="N86" s="4" t="inlineStr">
+      <c r="M86" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O86" s="4" t="inlineStr">
         <is>
           <t>11.5</t>
         </is>
@@ -6188,8 +6853,17 @@
           <t>69.2</t>
         </is>
       </c>
-      <c r="M87" s="6" t="inlineStr"/>
-      <c r="N87" s="6" t="inlineStr">
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O87" s="6" t="inlineStr">
         <is>
           <t>19.8</t>
         </is>
@@ -6256,8 +6930,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M88" s="4" t="inlineStr"/>
-      <c r="N88" s="4" t="inlineStr">
+      <c r="M88" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O88" s="4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -6324,8 +7007,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M89" s="6" t="inlineStr"/>
-      <c r="N89" s="6" t="inlineStr">
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O89" s="6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
@@ -6392,8 +7084,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M90" s="4" t="inlineStr"/>
-      <c r="N90" s="4" t="inlineStr">
+      <c r="M90" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O90" s="4" t="inlineStr">
         <is>
           <t>14.9</t>
         </is>
@@ -6460,8 +7161,17 @@
           <t>69.2</t>
         </is>
       </c>
-      <c r="M91" s="6" t="inlineStr"/>
-      <c r="N91" s="6" t="inlineStr">
+      <c r="M91" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O91" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -6528,8 +7238,17 @@
           <t>68.7</t>
         </is>
       </c>
-      <c r="M92" s="4" t="inlineStr"/>
-      <c r="N92" s="4" t="inlineStr">
+      <c r="M92" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O92" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -6584,8 +7303,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M93" s="6" t="inlineStr"/>
-      <c r="N93" s="6" t="inlineStr">
+      <c r="M93" s="6" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O93" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -6652,8 +7380,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M94" s="4" t="inlineStr"/>
-      <c r="N94" s="4" t="inlineStr">
+      <c r="M94" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="O94" s="4" t="inlineStr">
         <is>
           <t>13.7</t>
         </is>
@@ -6720,8 +7457,17 @@
           <t>37.5</t>
         </is>
       </c>
-      <c r="M95" s="6" t="inlineStr"/>
-      <c r="N95" s="6" t="inlineStr">
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O95" s="6" t="inlineStr">
         <is>
           <t>12.9</t>
         </is>
@@ -6788,8 +7534,17 @@
           <t>22.2</t>
         </is>
       </c>
-      <c r="M96" s="4" t="inlineStr"/>
-      <c r="N96" s="4" t="inlineStr">
+      <c r="M96" s="4" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O96" s="4" t="inlineStr">
         <is>
           <t>16.8</t>
         </is>
@@ -6856,8 +7611,17 @@
           <t>42.1</t>
         </is>
       </c>
-      <c r="M97" s="6" t="inlineStr"/>
-      <c r="N97" s="6" t="inlineStr">
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="O97" s="6" t="inlineStr">
         <is>
           <t>12.9</t>
         </is>
@@ -6924,8 +7688,17 @@
           <t>61.5</t>
         </is>
       </c>
-      <c r="M98" s="4" t="inlineStr"/>
-      <c r="N98" s="4" t="inlineStr">
+      <c r="M98" s="4" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O98" s="4" t="inlineStr">
         <is>
           <t>10.9</t>
         </is>
@@ -6992,8 +7765,17 @@
           <t>59.3</t>
         </is>
       </c>
-      <c r="M99" s="6" t="inlineStr"/>
-      <c r="N99" s="6" t="inlineStr">
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O99" s="6" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
@@ -7060,8 +7842,17 @@
           <t>55.6</t>
         </is>
       </c>
-      <c r="M100" s="4" t="inlineStr"/>
-      <c r="N100" s="4" t="inlineStr">
+      <c r="M100" s="4" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O100" s="4" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
@@ -7128,8 +7919,17 @@
           <t>72.2</t>
         </is>
       </c>
-      <c r="M101" s="6" t="inlineStr"/>
-      <c r="N101" s="6" t="inlineStr">
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="O101" s="6" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -7196,8 +7996,17 @@
           <t>78.6</t>
         </is>
       </c>
-      <c r="M102" s="4" t="inlineStr"/>
-      <c r="N102" s="4" t="inlineStr">
+      <c r="M102" s="4" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O102" s="4" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -7264,8 +8073,17 @@
           <t>50</t>
         </is>
       </c>
-      <c r="M103" s="6" t="inlineStr"/>
-      <c r="N103" s="6" t="inlineStr">
+      <c r="M103" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O103" s="6" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
@@ -7332,8 +8150,17 @@
           <t>44.2</t>
         </is>
       </c>
-      <c r="M104" s="4" t="inlineStr"/>
-      <c r="N104" s="4" t="inlineStr">
+      <c r="M104" s="4" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O104" s="4" t="inlineStr">
         <is>
           <t>12.7</t>
         </is>
@@ -7400,8 +8227,17 @@
           <t>85.7</t>
         </is>
       </c>
-      <c r="M105" s="6" t="inlineStr"/>
-      <c r="N105" s="6" t="inlineStr">
+      <c r="M105" s="6" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O105" s="6" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -7468,8 +8304,17 @@
           <t>92.9</t>
         </is>
       </c>
-      <c r="M106" s="4" t="inlineStr"/>
-      <c r="N106" s="4" t="inlineStr">
+      <c r="M106" s="4" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O106" s="4" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -7536,8 +8381,17 @@
           <t>83.3</t>
         </is>
       </c>
-      <c r="M107" s="6" t="inlineStr"/>
-      <c r="N107" s="6" t="inlineStr">
+      <c r="M107" s="6" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O107" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -7604,8 +8458,17 @@
           <t>83.3</t>
         </is>
       </c>
-      <c r="M108" s="4" t="inlineStr"/>
-      <c r="N108" s="4" t="inlineStr">
+      <c r="M108" s="4" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O108" s="4" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -7672,8 +8535,17 @@
           <t>81.8</t>
         </is>
       </c>
-      <c r="M109" s="6" t="inlineStr"/>
-      <c r="N109" s="6" t="inlineStr">
+      <c r="M109" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O109" s="6" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -7740,8 +8612,17 @@
           <t>90</t>
         </is>
       </c>
-      <c r="M110" s="4" t="inlineStr"/>
-      <c r="N110" s="4" t="inlineStr">
+      <c r="M110" s="4" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O110" s="4" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -7808,8 +8689,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M111" s="6" t="inlineStr"/>
-      <c r="N111" s="6" t="inlineStr">
+      <c r="M111" s="6" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O111" s="6" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -7876,8 +8766,17 @@
           <t>89.5</t>
         </is>
       </c>
-      <c r="M112" s="4" t="inlineStr"/>
-      <c r="N112" s="4" t="inlineStr">
+      <c r="M112" s="4" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O112" s="4" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
@@ -7944,8 +8843,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M113" s="6" t="inlineStr"/>
-      <c r="N113" s="6" t="inlineStr">
+      <c r="M113" s="6" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O113" s="6" t="inlineStr">
         <is>
           <t>6.9</t>
         </is>
@@ -8012,8 +8920,17 @@
           <t>80</t>
         </is>
       </c>
-      <c r="M114" s="4" t="inlineStr"/>
-      <c r="N114" s="4" t="inlineStr">
+      <c r="M114" s="4" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O114" s="4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -8080,8 +8997,17 @@
           <t>85.7</t>
         </is>
       </c>
-      <c r="M115" s="6" t="inlineStr"/>
-      <c r="N115" s="6" t="inlineStr">
+      <c r="M115" s="6" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O115" s="6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -8148,8 +9074,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="M116" s="4" t="inlineStr"/>
-      <c r="N116" s="4" t="inlineStr">
+      <c r="M116" s="4" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="O116" s="4" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -8216,8 +9151,17 @@
           <t>89.3</t>
         </is>
       </c>
-      <c r="M117" s="6" t="inlineStr"/>
-      <c r="N117" s="6" t="inlineStr">
+      <c r="M117" s="6" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="O117" s="6" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -8284,8 +9228,17 @@
           <t>43.5</t>
         </is>
       </c>
-      <c r="M118" s="4" t="inlineStr"/>
-      <c r="N118" s="4" t="inlineStr">
+      <c r="M118" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O118" s="4" t="inlineStr">
         <is>
           <t>12.6</t>
         </is>
@@ -8352,8 +9305,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="M119" s="6" t="inlineStr"/>
-      <c r="N119" s="6" t="inlineStr">
+      <c r="M119" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O119" s="6" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
@@ -8420,8 +9382,17 @@
           <t>80</t>
         </is>
       </c>
-      <c r="M120" s="4" t="inlineStr"/>
-      <c r="N120" s="4" t="inlineStr">
+      <c r="M120" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O120" s="4" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -8488,8 +9459,17 @@
           <t>62.5</t>
         </is>
       </c>
-      <c r="M121" s="6" t="inlineStr"/>
-      <c r="N121" s="6" t="inlineStr">
+      <c r="M121" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O121" s="6" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
@@ -8556,8 +9536,17 @@
           <t>61.5</t>
         </is>
       </c>
-      <c r="M122" s="4" t="inlineStr"/>
-      <c r="N122" s="4" t="inlineStr">
+      <c r="M122" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O122" s="4" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -8624,8 +9613,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M123" s="6" t="inlineStr"/>
-      <c r="N123" s="6" t="inlineStr">
+      <c r="M123" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O123" s="6" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -8692,8 +9690,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M124" s="4" t="inlineStr"/>
-      <c r="N124" s="4" t="inlineStr">
+      <c r="M124" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O124" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -8760,8 +9767,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M125" s="6" t="inlineStr"/>
-      <c r="N125" s="6" t="inlineStr">
+      <c r="M125" s="6" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="O125" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -8828,8 +9844,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M126" s="4" t="inlineStr"/>
-      <c r="N126" s="4" t="inlineStr">
+      <c r="M126" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O126" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -8896,8 +9921,17 @@
           <t>53.8</t>
         </is>
       </c>
-      <c r="M127" s="6" t="inlineStr"/>
-      <c r="N127" s="6" t="inlineStr">
+      <c r="M127" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O127" s="6" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -8964,8 +9998,17 @@
           <t>25</t>
         </is>
       </c>
-      <c r="M128" s="4" t="inlineStr"/>
-      <c r="N128" s="4" t="inlineStr">
+      <c r="M128" s="4" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O128" s="4" t="inlineStr">
         <is>
           <t>11.3</t>
         </is>
@@ -9032,8 +10075,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M129" s="6" t="inlineStr"/>
-      <c r="N129" s="6" t="inlineStr">
+      <c r="M129" s="6" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="O129" s="6" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -9100,8 +10152,17 @@
           <t>10</t>
         </is>
       </c>
-      <c r="M130" s="4" t="inlineStr"/>
-      <c r="N130" s="4" t="inlineStr">
+      <c r="M130" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O130" s="4" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
@@ -9168,8 +10229,17 @@
           <t>24</t>
         </is>
       </c>
-      <c r="M131" s="6" t="inlineStr"/>
-      <c r="N131" s="6" t="inlineStr">
+      <c r="M131" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O131" s="6" t="inlineStr">
         <is>
           <t>15.3</t>
         </is>
@@ -9236,8 +10306,17 @@
           <t>62.5</t>
         </is>
       </c>
-      <c r="M132" s="4" t="inlineStr"/>
-      <c r="N132" s="4" t="inlineStr">
+      <c r="M132" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O132" s="4" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -9304,8 +10383,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="M133" s="6" t="inlineStr"/>
-      <c r="N133" s="6" t="inlineStr">
+      <c r="M133" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O133" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -9372,8 +10460,17 @@
           <t>72.2</t>
         </is>
       </c>
-      <c r="M134" s="4" t="inlineStr"/>
-      <c r="N134" s="4" t="inlineStr">
+      <c r="M134" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O134" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -9440,8 +10537,17 @@
           <t>81.5</t>
         </is>
       </c>
-      <c r="M135" s="6" t="inlineStr"/>
-      <c r="N135" s="6" t="inlineStr">
+      <c r="M135" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O135" s="6" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
@@ -9508,8 +10614,17 @@
           <t>75</t>
         </is>
       </c>
-      <c r="M136" s="4" t="inlineStr"/>
-      <c r="N136" s="4" t="inlineStr">
+      <c r="M136" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O136" s="4" t="inlineStr">
         <is>
           <t>43.7</t>
         </is>
@@ -9576,8 +10691,17 @@
           <t>75</t>
         </is>
       </c>
-      <c r="M137" s="6" t="inlineStr"/>
-      <c r="N137" s="6" t="inlineStr">
+      <c r="M137" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O137" s="6" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
@@ -9644,8 +10768,17 @@
           <t>14.3</t>
         </is>
       </c>
-      <c r="M138" s="4" t="inlineStr"/>
-      <c r="N138" s="4" t="inlineStr">
+      <c r="M138" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O138" s="4" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -9712,8 +10845,17 @@
           <t>76</t>
         </is>
       </c>
-      <c r="M139" s="6" t="inlineStr"/>
-      <c r="N139" s="6" t="inlineStr">
+      <c r="M139" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O139" s="6" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
@@ -9780,8 +10922,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M140" s="4" t="inlineStr"/>
-      <c r="N140" s="4" t="inlineStr">
+      <c r="M140" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O140" s="4" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
@@ -9848,8 +10999,17 @@
           <t>59.6</t>
         </is>
       </c>
-      <c r="M141" s="6" t="inlineStr"/>
-      <c r="N141" s="6" t="inlineStr">
+      <c r="M141" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O141" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -9916,8 +11076,17 @@
           <t>28.6</t>
         </is>
       </c>
-      <c r="M142" s="4" t="inlineStr"/>
-      <c r="N142" s="4" t="inlineStr">
+      <c r="M142" s="4" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O142" s="4" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
@@ -9984,8 +11153,17 @@
           <t>80</t>
         </is>
       </c>
-      <c r="M143" s="6" t="inlineStr"/>
-      <c r="N143" s="6" t="inlineStr">
+      <c r="M143" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O143" s="6" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
@@ -10052,8 +11230,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="M144" s="4" t="inlineStr"/>
-      <c r="N144" s="4" t="inlineStr">
+      <c r="M144" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O144" s="4" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -10120,8 +11307,17 @@
           <t>72</t>
         </is>
       </c>
-      <c r="M145" s="6" t="inlineStr"/>
-      <c r="N145" s="6" t="inlineStr">
+      <c r="M145" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O145" s="6" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -10188,8 +11384,17 @@
           <t>60</t>
         </is>
       </c>
-      <c r="M146" s="4" t="inlineStr"/>
-      <c r="N146" s="4" t="inlineStr">
+      <c r="M146" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O146" s="4" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -10256,8 +11461,17 @@
           <t>86.4</t>
         </is>
       </c>
-      <c r="M147" s="6" t="inlineStr"/>
-      <c r="N147" s="6" t="inlineStr">
+      <c r="M147" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="O147" s="6" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
@@ -10324,8 +11538,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="M148" s="4" t="inlineStr"/>
-      <c r="N148" s="4" t="inlineStr">
+      <c r="M148" s="4" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O148" s="4" t="inlineStr">
         <is>
           <t>11.3</t>
         </is>
@@ -10392,8 +11615,17 @@
           <t>73.7</t>
         </is>
       </c>
-      <c r="M149" s="6" t="inlineStr"/>
-      <c r="N149" s="6" t="inlineStr">
+      <c r="M149" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="O149" s="6" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -10460,8 +11692,17 @@
           <t>25</t>
         </is>
       </c>
-      <c r="M150" s="4" t="inlineStr"/>
-      <c r="N150" s="4" t="inlineStr">
+      <c r="M150" s="4" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O150" s="4" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -10528,8 +11769,17 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="M151" s="6" t="inlineStr"/>
-      <c r="N151" s="6" t="inlineStr">
+      <c r="M151" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O151" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -10596,8 +11846,17 @@
           <t>88.6</t>
         </is>
       </c>
-      <c r="M152" s="4" t="inlineStr"/>
-      <c r="N152" s="4" t="inlineStr">
+      <c r="M152" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O152" s="4" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -10664,8 +11923,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="M153" s="6" t="inlineStr"/>
-      <c r="N153" s="6" t="inlineStr">
+      <c r="M153" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O153" s="6" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -10732,8 +12000,17 @@
           <t>61.1</t>
         </is>
       </c>
-      <c r="M154" s="4" t="inlineStr"/>
-      <c r="N154" s="4" t="inlineStr">
+      <c r="M154" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="O154" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -10800,8 +12077,17 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="M155" s="6" t="inlineStr"/>
-      <c r="N155" s="6" t="inlineStr">
+      <c r="M155" s="6" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O155" s="6" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -10868,8 +12154,17 @@
           <t>69.4</t>
         </is>
       </c>
-      <c r="M156" s="4" t="inlineStr"/>
-      <c r="N156" s="4" t="inlineStr">
+      <c r="M156" s="4" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O156" s="4" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
@@ -10936,8 +12231,17 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="M157" s="6" t="inlineStr"/>
-      <c r="N157" s="6" t="inlineStr">
+      <c r="M157" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O157" s="6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -11005,7 +12309,8 @@
         </is>
       </c>
       <c r="M158" s="4" t="inlineStr"/>
-      <c r="N158" s="4" t="inlineStr">
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -11073,7 +12378,8 @@
         </is>
       </c>
       <c r="M159" s="6" t="inlineStr"/>
-      <c r="N159" s="6" t="inlineStr">
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" s="6" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -11128,8 +12434,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M160" s="4" t="inlineStr"/>
-      <c r="N160" s="4" t="inlineStr">
+      <c r="M160" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" s="4" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -11196,8 +12507,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M161" s="6" t="inlineStr"/>
-      <c r="N161" s="6" t="inlineStr">
+      <c r="M161" s="6" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -11265,7 +12581,8 @@
         </is>
       </c>
       <c r="M162" s="4" t="inlineStr"/>
-      <c r="N162" s="4" t="inlineStr">
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -11333,7 +12650,8 @@
         </is>
       </c>
       <c r="M163" s="6" t="inlineStr"/>
-      <c r="N163" s="6" t="inlineStr">
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" s="6" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -11401,7 +12719,8 @@
         </is>
       </c>
       <c r="M164" s="4" t="inlineStr"/>
-      <c r="N164" s="4" t="inlineStr">
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" s="4" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
@@ -11469,7 +12788,8 @@
         </is>
       </c>
       <c r="M165" s="6" t="inlineStr"/>
-      <c r="N165" s="6" t="inlineStr">
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" s="6" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -11537,7 +12857,8 @@
         </is>
       </c>
       <c r="M166" s="4" t="inlineStr"/>
-      <c r="N166" s="4" t="inlineStr">
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" s="4" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -11605,7 +12926,8 @@
         </is>
       </c>
       <c r="M167" s="6" t="inlineStr"/>
-      <c r="N167" s="6" t="inlineStr">
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" s="6" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -11673,7 +12995,8 @@
         </is>
       </c>
       <c r="M168" s="4" t="inlineStr"/>
-      <c r="N168" s="4" t="inlineStr">
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -11741,7 +13064,8 @@
         </is>
       </c>
       <c r="M169" s="6" t="inlineStr"/>
-      <c r="N169" s="6" t="inlineStr">
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -11809,7 +13133,8 @@
         </is>
       </c>
       <c r="M170" s="4" t="inlineStr"/>
-      <c r="N170" s="4" t="inlineStr">
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" s="4" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
@@ -11877,7 +13202,8 @@
         </is>
       </c>
       <c r="M171" s="6" t="inlineStr"/>
-      <c r="N171" s="6" t="inlineStr">
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -11945,7 +13271,8 @@
         </is>
       </c>
       <c r="M172" s="4" t="inlineStr"/>
-      <c r="N172" s="4" t="inlineStr">
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -12013,7 +13340,8 @@
         </is>
       </c>
       <c r="M173" s="6" t="inlineStr"/>
-      <c r="N173" s="6" t="inlineStr">
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -12081,7 +13409,8 @@
         </is>
       </c>
       <c r="M174" s="4" t="inlineStr"/>
-      <c r="N174" s="4" t="inlineStr">
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" s="4" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -12149,7 +13478,8 @@
         </is>
       </c>
       <c r="M175" s="6" t="inlineStr"/>
-      <c r="N175" s="6" t="inlineStr">
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" s="6" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
@@ -12217,7 +13547,8 @@
         </is>
       </c>
       <c r="M176" s="4" t="inlineStr"/>
-      <c r="N176" s="4" t="inlineStr">
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" s="4" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -12285,7 +13616,8 @@
         </is>
       </c>
       <c r="M177" s="6" t="inlineStr"/>
-      <c r="N177" s="6" t="inlineStr">
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" s="6" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -12353,7 +13685,8 @@
         </is>
       </c>
       <c r="M178" s="4" t="inlineStr"/>
-      <c r="N178" s="4" t="inlineStr">
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" s="4" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -12421,7 +13754,8 @@
         </is>
       </c>
       <c r="M179" s="6" t="inlineStr"/>
-      <c r="N179" s="6" t="inlineStr">
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -12489,7 +13823,8 @@
         </is>
       </c>
       <c r="M180" s="4" t="inlineStr"/>
-      <c r="N180" s="4" t="inlineStr">
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -12557,7 +13892,8 @@
         </is>
       </c>
       <c r="M181" s="6" t="inlineStr"/>
-      <c r="N181" s="6" t="inlineStr">
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" s="6" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -12625,7 +13961,8 @@
         </is>
       </c>
       <c r="M182" s="4" t="inlineStr"/>
-      <c r="N182" s="4" t="inlineStr">
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" s="4" t="inlineStr">
         <is>
           <t>1.9</t>
         </is>
@@ -12693,7 +14030,8 @@
         </is>
       </c>
       <c r="M183" s="6" t="inlineStr"/>
-      <c r="N183" s="6" t="inlineStr">
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" s="6" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
@@ -12761,7 +14099,8 @@
         </is>
       </c>
       <c r="M184" s="4" t="inlineStr"/>
-      <c r="N184" s="4" t="inlineStr">
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" s="4" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -12829,7 +14168,8 @@
         </is>
       </c>
       <c r="M185" s="6" t="inlineStr"/>
-      <c r="N185" s="6" t="inlineStr">
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" s="6" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -12897,7 +14237,8 @@
         </is>
       </c>
       <c r="M186" s="4" t="inlineStr"/>
-      <c r="N186" s="4" t="inlineStr">
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" s="4" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
@@ -12965,7 +14306,8 @@
         </is>
       </c>
       <c r="M187" s="6" t="inlineStr"/>
-      <c r="N187" s="6" t="inlineStr">
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -13033,7 +14375,8 @@
         </is>
       </c>
       <c r="M188" s="4" t="inlineStr"/>
-      <c r="N188" s="4" t="inlineStr">
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -13101,7 +14444,8 @@
         </is>
       </c>
       <c r="M189" s="6" t="inlineStr"/>
-      <c r="N189" s="6" t="inlineStr">
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -13169,7 +14513,8 @@
         </is>
       </c>
       <c r="M190" s="4" t="inlineStr"/>
-      <c r="N190" s="4" t="inlineStr">
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" s="4" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -13237,7 +14582,8 @@
         </is>
       </c>
       <c r="M191" s="6" t="inlineStr"/>
-      <c r="N191" s="6" t="inlineStr">
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" s="6" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -13305,7 +14651,8 @@
         </is>
       </c>
       <c r="M192" s="4" t="inlineStr"/>
-      <c r="N192" s="4" t="inlineStr">
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" s="4" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
@@ -13373,7 +14720,8 @@
         </is>
       </c>
       <c r="M193" s="6" t="inlineStr"/>
-      <c r="N193" s="6" t="inlineStr">
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" s="6" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -13441,7 +14789,8 @@
         </is>
       </c>
       <c r="M194" s="4" t="inlineStr"/>
-      <c r="N194" s="4" t="inlineStr">
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" s="4" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -13509,7 +14858,8 @@
         </is>
       </c>
       <c r="M195" s="6" t="inlineStr"/>
-      <c r="N195" s="6" t="inlineStr">
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" s="6" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -13577,7 +14927,8 @@
         </is>
       </c>
       <c r="M196" s="4" t="inlineStr"/>
-      <c r="N196" s="4" t="inlineStr">
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" s="4" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -13645,7 +14996,8 @@
         </is>
       </c>
       <c r="M197" s="6" t="inlineStr"/>
-      <c r="N197" s="6" t="inlineStr">
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -13713,7 +15065,8 @@
         </is>
       </c>
       <c r="M198" s="4" t="inlineStr"/>
-      <c r="N198" s="4" t="inlineStr">
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" s="4" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -13781,7 +15134,8 @@
         </is>
       </c>
       <c r="M199" s="6" t="inlineStr"/>
-      <c r="N199" s="6" t="inlineStr">
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" s="6" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
@@ -13849,7 +15203,8 @@
         </is>
       </c>
       <c r="M200" s="4" t="inlineStr"/>
-      <c r="N200" s="4" t="inlineStr">
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -13917,7 +15272,8 @@
         </is>
       </c>
       <c r="M201" s="6" t="inlineStr"/>
-      <c r="N201" s="6" t="inlineStr">
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" s="6" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -13985,7 +15341,8 @@
         </is>
       </c>
       <c r="M202" s="4" t="inlineStr"/>
-      <c r="N202" s="4" t="inlineStr">
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" s="4" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -14053,7 +15410,8 @@
         </is>
       </c>
       <c r="M203" s="6" t="inlineStr"/>
-      <c r="N203" s="6" t="inlineStr">
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -14121,7 +15479,8 @@
         </is>
       </c>
       <c r="M204" s="4" t="inlineStr"/>
-      <c r="N204" s="4" t="inlineStr">
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -14189,7 +15548,8 @@
         </is>
       </c>
       <c r="M205" s="6" t="inlineStr"/>
-      <c r="N205" s="6" t="inlineStr">
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -14257,7 +15617,8 @@
         </is>
       </c>
       <c r="M206" s="4" t="inlineStr"/>
-      <c r="N206" s="4" t="inlineStr">
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" s="4" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
@@ -14325,7 +15686,8 @@
         </is>
       </c>
       <c r="M207" s="6" t="inlineStr"/>
-      <c r="N207" s="6" t="inlineStr">
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -14393,7 +15755,8 @@
         </is>
       </c>
       <c r="M208" s="4" t="inlineStr"/>
-      <c r="N208" s="4" t="inlineStr">
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" s="4" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -14461,7 +15824,8 @@
         </is>
       </c>
       <c r="M209" s="6" t="inlineStr"/>
-      <c r="N209" s="6" t="inlineStr">
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -14529,7 +15893,8 @@
         </is>
       </c>
       <c r="M210" s="4" t="inlineStr"/>
-      <c r="N210" s="4" t="inlineStr">
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -14597,7 +15962,8 @@
         </is>
       </c>
       <c r="M211" s="6" t="inlineStr"/>
-      <c r="N211" s="6" t="inlineStr">
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" s="6" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -14665,7 +16031,8 @@
         </is>
       </c>
       <c r="M212" s="4" t="inlineStr"/>
-      <c r="N212" s="4" t="inlineStr">
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" s="4" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -14733,7 +16100,8 @@
         </is>
       </c>
       <c r="M213" s="6" t="inlineStr"/>
-      <c r="N213" s="6" t="inlineStr">
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -14801,7 +16169,8 @@
         </is>
       </c>
       <c r="M214" s="4" t="inlineStr"/>
-      <c r="N214" s="4" t="inlineStr">
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" s="4" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -14869,7 +16238,8 @@
         </is>
       </c>
       <c r="M215" s="6" t="inlineStr"/>
-      <c r="N215" s="6" t="inlineStr">
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" s="6" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -14937,7 +16307,8 @@
         </is>
       </c>
       <c r="M216" s="4" t="inlineStr"/>
-      <c r="N216" s="4" t="inlineStr">
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -15005,7 +16376,8 @@
         </is>
       </c>
       <c r="M217" s="6" t="inlineStr"/>
-      <c r="N217" s="6" t="inlineStr">
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" s="6" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -15073,7 +16445,8 @@
         </is>
       </c>
       <c r="M218" s="4" t="inlineStr"/>
-      <c r="N218" s="4" t="inlineStr">
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" s="4" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
@@ -15141,7 +16514,8 @@
         </is>
       </c>
       <c r="M219" s="6" t="inlineStr"/>
-      <c r="N219" s="6" t="inlineStr">
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -15209,7 +16583,8 @@
         </is>
       </c>
       <c r="M220" s="4" t="inlineStr"/>
-      <c r="N220" s="4" t="inlineStr">
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -15277,7 +16652,8 @@
         </is>
       </c>
       <c r="M221" s="6" t="inlineStr"/>
-      <c r="N221" s="6" t="inlineStr">
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" s="6" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
@@ -15345,7 +16721,8 @@
         </is>
       </c>
       <c r="M222" s="4" t="inlineStr"/>
-      <c r="N222" s="4" t="inlineStr">
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" s="4" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -15413,7 +16790,8 @@
         </is>
       </c>
       <c r="M223" s="6" t="inlineStr"/>
-      <c r="N223" s="6" t="inlineStr">
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -15481,7 +16859,8 @@
         </is>
       </c>
       <c r="M224" s="4" t="inlineStr"/>
-      <c r="N224" s="4" t="inlineStr">
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -15545,7 +16924,8 @@
       </c>
       <c r="L225" s="6" t="inlineStr"/>
       <c r="M225" s="6" t="inlineStr"/>
-      <c r="N225" s="6" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" s="6" t="inlineStr"/>
     </row>
     <row r="226" ht="32" customHeight="1">
       <c r="A226" s="3" t="inlineStr">
@@ -15596,8 +16976,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M226" s="4" t="inlineStr"/>
-      <c r="N226" s="4" t="inlineStr">
+      <c r="M226" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -15648,8 +17033,13 @@
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr"/>
-      <c r="M227" s="6" t="inlineStr"/>
-      <c r="N227" s="6" t="inlineStr"/>
+      <c r="M227" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" s="6" t="inlineStr"/>
     </row>
     <row r="228" ht="32" customHeight="1">
       <c r="A228" s="3" t="inlineStr">
@@ -15696,8 +17086,13 @@
         </is>
       </c>
       <c r="L228" s="4" t="inlineStr"/>
-      <c r="M228" s="4" t="inlineStr"/>
-      <c r="N228" s="4" t="inlineStr"/>
+      <c r="M228" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" s="4" t="inlineStr"/>
     </row>
     <row r="229" ht="32" customHeight="1">
       <c r="A229" s="5" t="inlineStr">
@@ -15744,8 +17139,13 @@
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr"/>
-      <c r="M229" s="6" t="inlineStr"/>
-      <c r="N229" s="6" t="inlineStr"/>
+      <c r="M229" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" s="6" t="inlineStr"/>
     </row>
     <row r="230" ht="32" customHeight="1">
       <c r="A230" s="3" t="inlineStr">
@@ -15792,8 +17192,13 @@
         </is>
       </c>
       <c r="L230" s="4" t="inlineStr"/>
-      <c r="M230" s="4" t="inlineStr"/>
-      <c r="N230" s="4" t="inlineStr"/>
+      <c r="M230" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" s="4" t="inlineStr"/>
     </row>
     <row r="231" ht="32" customHeight="1">
       <c r="A231" s="5" t="inlineStr">
@@ -15840,8 +17245,13 @@
         </is>
       </c>
       <c r="L231" s="6" t="inlineStr"/>
-      <c r="M231" s="6" t="inlineStr"/>
-      <c r="N231" s="6" t="inlineStr"/>
+      <c r="M231" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" s="6" t="inlineStr"/>
     </row>
     <row r="232" ht="32" customHeight="1">
       <c r="A232" s="3" t="inlineStr">
@@ -15888,8 +17298,13 @@
         </is>
       </c>
       <c r="L232" s="4" t="inlineStr"/>
-      <c r="M232" s="4" t="inlineStr"/>
-      <c r="N232" s="4" t="inlineStr"/>
+      <c r="M232" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" s="4" t="inlineStr"/>
     </row>
     <row r="233" ht="32" customHeight="1">
       <c r="A233" s="5" t="inlineStr">
@@ -15936,8 +17351,13 @@
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr"/>
-      <c r="M233" s="6" t="inlineStr"/>
-      <c r="N233" s="6" t="inlineStr"/>
+      <c r="M233" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" s="6" t="inlineStr"/>
     </row>
     <row r="234" ht="32" customHeight="1">
       <c r="A234" s="3" t="inlineStr">
@@ -15984,8 +17404,13 @@
         </is>
       </c>
       <c r="L234" s="4" t="inlineStr"/>
-      <c r="M234" s="4" t="inlineStr"/>
-      <c r="N234" s="4" t="inlineStr"/>
+      <c r="M234" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" s="4" t="inlineStr"/>
     </row>
     <row r="235" ht="32" customHeight="1">
       <c r="A235" s="5" t="inlineStr">
@@ -16032,8 +17457,13 @@
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr"/>
-      <c r="M235" s="6" t="inlineStr"/>
-      <c r="N235" s="6" t="inlineStr"/>
+      <c r="M235" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" s="6" t="inlineStr"/>
     </row>
     <row r="236" ht="32" customHeight="1">
       <c r="A236" s="3" t="inlineStr">
@@ -16080,8 +17510,13 @@
         </is>
       </c>
       <c r="L236" s="4" t="inlineStr"/>
-      <c r="M236" s="4" t="inlineStr"/>
-      <c r="N236" s="4" t="inlineStr"/>
+      <c r="M236" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" s="4" t="inlineStr"/>
     </row>
     <row r="237" ht="32" customHeight="1">
       <c r="A237" s="5" t="inlineStr">
@@ -16128,8 +17563,13 @@
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr"/>
-      <c r="M237" s="6" t="inlineStr"/>
-      <c r="N237" s="6" t="inlineStr"/>
+      <c r="M237" s="6" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" s="6" t="inlineStr"/>
     </row>
     <row r="238" ht="32" customHeight="1">
       <c r="A238" s="3" t="inlineStr">
@@ -16176,8 +17616,13 @@
         </is>
       </c>
       <c r="L238" s="4" t="inlineStr"/>
-      <c r="M238" s="4" t="inlineStr"/>
-      <c r="N238" s="4" t="inlineStr"/>
+      <c r="M238" s="4" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" s="4" t="inlineStr"/>
     </row>
     <row r="239" ht="32" customHeight="1">
       <c r="A239" s="5" t="inlineStr">
@@ -16224,8 +17669,13 @@
         </is>
       </c>
       <c r="L239" s="6" t="inlineStr"/>
-      <c r="M239" s="6" t="inlineStr"/>
-      <c r="N239" s="6" t="inlineStr"/>
+      <c r="M239" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" s="6" t="inlineStr"/>
     </row>
     <row r="240" ht="32" customHeight="1">
       <c r="A240" s="3" t="inlineStr">
@@ -16276,8 +17726,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M240" s="4" t="inlineStr"/>
-      <c r="N240" s="4" t="inlineStr">
+      <c r="M240" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -16332,8 +17787,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M241" s="6" t="inlineStr"/>
-      <c r="N241" s="6" t="inlineStr">
+      <c r="M241" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -16384,8 +17844,13 @@
         </is>
       </c>
       <c r="L242" s="4" t="inlineStr"/>
-      <c r="M242" s="4" t="inlineStr"/>
-      <c r="N242" s="4" t="inlineStr"/>
+      <c r="M242" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" s="4" t="inlineStr"/>
     </row>
     <row r="243" ht="32" customHeight="1">
       <c r="A243" s="5" t="inlineStr">
@@ -16432,8 +17897,13 @@
         </is>
       </c>
       <c r="L243" s="6" t="inlineStr"/>
-      <c r="M243" s="6" t="inlineStr"/>
-      <c r="N243" s="6" t="inlineStr"/>
+      <c r="M243" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" s="6" t="inlineStr"/>
     </row>
     <row r="244" ht="32" customHeight="1">
       <c r="A244" s="3" t="inlineStr">
@@ -16480,8 +17950,13 @@
         </is>
       </c>
       <c r="L244" s="4" t="inlineStr"/>
-      <c r="M244" s="4" t="inlineStr"/>
-      <c r="N244" s="4" t="inlineStr"/>
+      <c r="M244" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" s="4" t="inlineStr"/>
     </row>
     <row r="245" ht="32" customHeight="1">
       <c r="A245" s="5" t="inlineStr">
@@ -16528,8 +18003,13 @@
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr"/>
-      <c r="M245" s="6" t="inlineStr"/>
-      <c r="N245" s="6" t="inlineStr"/>
+      <c r="M245" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" s="6" t="inlineStr"/>
     </row>
     <row r="246" ht="32" customHeight="1">
       <c r="A246" s="3" t="inlineStr">
@@ -16580,8 +18060,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M246" s="4" t="inlineStr"/>
-      <c r="N246" s="4" t="inlineStr">
+      <c r="M246" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -16632,8 +18117,13 @@
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr"/>
-      <c r="M247" s="6" t="inlineStr"/>
-      <c r="N247" s="6" t="inlineStr"/>
+      <c r="M247" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" s="6" t="inlineStr"/>
     </row>
     <row r="248" ht="32" customHeight="1">
       <c r="A248" s="3" t="inlineStr">
@@ -16680,8 +18170,13 @@
         </is>
       </c>
       <c r="L248" s="4" t="inlineStr"/>
-      <c r="M248" s="4" t="inlineStr"/>
-      <c r="N248" s="4" t="inlineStr"/>
+      <c r="M248" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" s="4" t="inlineStr"/>
     </row>
     <row r="249" ht="32" customHeight="1">
       <c r="A249" s="5" t="inlineStr">
@@ -16732,8 +18227,13 @@
           <t>40</t>
         </is>
       </c>
-      <c r="M249" s="6" t="inlineStr"/>
-      <c r="N249" s="6" t="inlineStr">
+      <c r="M249" s="6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" s="6" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -16788,8 +18288,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M250" s="4" t="inlineStr"/>
-      <c r="N250" s="4" t="inlineStr">
+      <c r="M250" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -16840,8 +18345,13 @@
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr"/>
-      <c r="M251" s="6" t="inlineStr"/>
-      <c r="N251" s="6" t="inlineStr"/>
+      <c r="M251" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" s="6" t="inlineStr"/>
     </row>
     <row r="252" ht="32" customHeight="1">
       <c r="A252" s="3" t="inlineStr">
@@ -16888,8 +18398,13 @@
         </is>
       </c>
       <c r="L252" s="4" t="inlineStr"/>
-      <c r="M252" s="4" t="inlineStr"/>
-      <c r="N252" s="4" t="inlineStr"/>
+      <c r="M252" s="4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" s="4" t="inlineStr"/>
     </row>
     <row r="253" ht="32" customHeight="1">
       <c r="A253" s="5" t="inlineStr">
@@ -16936,8 +18451,13 @@
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr"/>
-      <c r="M253" s="6" t="inlineStr"/>
-      <c r="N253" s="6" t="inlineStr"/>
+      <c r="M253" s="6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" s="6" t="inlineStr"/>
     </row>
     <row r="254" ht="32" customHeight="1">
       <c r="A254" s="3" t="inlineStr">
@@ -16984,8 +18504,13 @@
         </is>
       </c>
       <c r="L254" s="4" t="inlineStr"/>
-      <c r="M254" s="4" t="inlineStr"/>
-      <c r="N254" s="4" t="inlineStr"/>
+      <c r="M254" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" s="4" t="inlineStr"/>
     </row>
     <row r="255" ht="32" customHeight="1">
       <c r="A255" s="5" t="inlineStr">
@@ -17032,8 +18557,13 @@
         </is>
       </c>
       <c r="L255" s="6" t="inlineStr"/>
-      <c r="M255" s="6" t="inlineStr"/>
-      <c r="N255" s="6" t="inlineStr"/>
+      <c r="M255" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" s="6" t="inlineStr"/>
     </row>
     <row r="256" ht="32" customHeight="1">
       <c r="A256" s="3" t="inlineStr">
@@ -17080,8 +18610,13 @@
         </is>
       </c>
       <c r="L256" s="4" t="inlineStr"/>
-      <c r="M256" s="4" t="inlineStr"/>
-      <c r="N256" s="4" t="inlineStr"/>
+      <c r="M256" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" s="4" t="inlineStr"/>
     </row>
     <row r="257" ht="32" customHeight="1">
       <c r="A257" s="5" t="inlineStr">
@@ -17132,8 +18667,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M257" s="6" t="inlineStr"/>
-      <c r="N257" s="6" t="inlineStr">
+      <c r="M257" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -17184,8 +18724,13 @@
         </is>
       </c>
       <c r="L258" s="4" t="inlineStr"/>
-      <c r="M258" s="4" t="inlineStr"/>
-      <c r="N258" s="4" t="inlineStr"/>
+      <c r="M258" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" s="4" t="inlineStr"/>
     </row>
     <row r="259" ht="32" customHeight="1">
       <c r="A259" s="5" t="inlineStr">
@@ -17232,8 +18777,13 @@
         </is>
       </c>
       <c r="L259" s="6" t="inlineStr"/>
-      <c r="M259" s="6" t="inlineStr"/>
-      <c r="N259" s="6" t="inlineStr"/>
+      <c r="M259" s="6" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" s="6" t="inlineStr"/>
     </row>
     <row r="260" ht="32" customHeight="1">
       <c r="A260" s="3" t="inlineStr">
@@ -17280,8 +18830,13 @@
         </is>
       </c>
       <c r="L260" s="4" t="inlineStr"/>
-      <c r="M260" s="4" t="inlineStr"/>
-      <c r="N260" s="4" t="inlineStr"/>
+      <c r="M260" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" s="4" t="inlineStr"/>
     </row>
     <row r="261" ht="32" customHeight="1">
       <c r="A261" s="5" t="inlineStr">
@@ -17328,8 +18883,13 @@
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr"/>
-      <c r="M261" s="6" t="inlineStr"/>
-      <c r="N261" s="6" t="inlineStr"/>
+      <c r="M261" s="6" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" s="6" t="inlineStr"/>
     </row>
     <row r="262" ht="32" customHeight="1">
       <c r="A262" s="3" t="inlineStr">
@@ -17380,8 +18940,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M262" s="4" t="inlineStr"/>
-      <c r="N262" s="4" t="inlineStr">
+      <c r="M262" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -17432,8 +18997,13 @@
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
-      <c r="M263" s="6" t="inlineStr"/>
-      <c r="N263" s="6" t="inlineStr"/>
+      <c r="M263" s="6" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" s="6" t="inlineStr"/>
     </row>
     <row r="264" ht="32" customHeight="1">
       <c r="A264" s="3" t="inlineStr">
@@ -17480,8 +19050,13 @@
         </is>
       </c>
       <c r="L264" s="4" t="inlineStr"/>
-      <c r="M264" s="4" t="inlineStr"/>
-      <c r="N264" s="4" t="inlineStr"/>
+      <c r="M264" s="4" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" s="4" t="inlineStr"/>
     </row>
     <row r="265" ht="32" customHeight="1">
       <c r="A265" s="5" t="inlineStr">
@@ -17532,8 +19107,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M265" s="6" t="inlineStr"/>
-      <c r="N265" s="6" t="inlineStr">
+      <c r="M265" s="6" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -17588,8 +19168,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M266" s="4" t="inlineStr"/>
-      <c r="N266" s="4" t="inlineStr">
+      <c r="M266" s="4" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -17640,8 +19225,13 @@
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
-      <c r="M267" s="6" t="inlineStr"/>
-      <c r="N267" s="6" t="inlineStr"/>
+      <c r="M267" s="6" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" s="6" t="inlineStr"/>
     </row>
     <row r="268" ht="32" customHeight="1">
       <c r="A268" s="3" t="inlineStr">
@@ -17692,8 +19282,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M268" s="4" t="inlineStr"/>
-      <c r="N268" s="4" t="inlineStr">
+      <c r="M268" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -17744,8 +19339,13 @@
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
-      <c r="M269" s="6" t="inlineStr"/>
-      <c r="N269" s="6" t="inlineStr"/>
+      <c r="M269" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" s="6" t="inlineStr"/>
     </row>
     <row r="270" ht="32" customHeight="1">
       <c r="A270" s="3" t="inlineStr">
@@ -17796,8 +19396,13 @@
           <t>57.1</t>
         </is>
       </c>
-      <c r="M270" s="4" t="inlineStr"/>
-      <c r="N270" s="4" t="inlineStr">
+      <c r="M270" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" s="4" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -17848,8 +19453,13 @@
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
-      <c r="M271" s="6" t="inlineStr"/>
-      <c r="N271" s="6" t="inlineStr"/>
+      <c r="M271" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" s="6" t="inlineStr"/>
     </row>
     <row r="272" ht="32" customHeight="1">
       <c r="A272" s="3" t="inlineStr">
@@ -17896,8 +19506,13 @@
         </is>
       </c>
       <c r="L272" s="4" t="inlineStr"/>
-      <c r="M272" s="4" t="inlineStr"/>
-      <c r="N272" s="4" t="inlineStr"/>
+      <c r="M272" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" s="4" t="inlineStr"/>
     </row>
     <row r="273" ht="32" customHeight="1">
       <c r="A273" s="5" t="inlineStr">
@@ -17944,8 +19559,13 @@
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
-      <c r="M273" s="6" t="inlineStr"/>
-      <c r="N273" s="6" t="inlineStr"/>
+      <c r="M273" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" s="6" t="inlineStr"/>
     </row>
     <row r="274" ht="32" customHeight="1">
       <c r="A274" s="3" t="inlineStr">
@@ -17992,8 +19612,13 @@
         </is>
       </c>
       <c r="L274" s="4" t="inlineStr"/>
-      <c r="M274" s="4" t="inlineStr"/>
-      <c r="N274" s="4" t="inlineStr"/>
+      <c r="M274" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" s="4" t="inlineStr"/>
     </row>
     <row r="275" ht="32" customHeight="1">
       <c r="A275" s="5" t="inlineStr">
@@ -18040,8 +19665,13 @@
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
-      <c r="M275" s="6" t="inlineStr"/>
-      <c r="N275" s="6" t="inlineStr"/>
+      <c r="M275" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" s="6" t="inlineStr"/>
     </row>
     <row r="276" ht="32" customHeight="1">
       <c r="A276" s="3" t="inlineStr">
@@ -18092,8 +19722,13 @@
           <t>50</t>
         </is>
       </c>
-      <c r="M276" s="4" t="inlineStr"/>
-      <c r="N276" s="4" t="inlineStr">
+      <c r="M276" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -18144,8 +19779,13 @@
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
-      <c r="M277" s="6" t="inlineStr"/>
-      <c r="N277" s="6" t="inlineStr"/>
+      <c r="M277" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" s="6" t="inlineStr"/>
     </row>
     <row r="278" ht="32" customHeight="1">
       <c r="A278" s="3" t="inlineStr">
@@ -18192,8 +19832,13 @@
         </is>
       </c>
       <c r="L278" s="4" t="inlineStr"/>
-      <c r="M278" s="4" t="inlineStr"/>
-      <c r="N278" s="4" t="inlineStr"/>
+      <c r="M278" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" s="4" t="inlineStr"/>
     </row>
     <row r="279" ht="32" customHeight="1">
       <c r="A279" s="5" t="inlineStr">
@@ -18240,8 +19885,13 @@
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
-      <c r="M279" s="6" t="inlineStr"/>
-      <c r="N279" s="6" t="inlineStr"/>
+      <c r="M279" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" s="6" t="inlineStr"/>
     </row>
     <row r="280" ht="32" customHeight="1">
       <c r="A280" s="3" t="inlineStr">
@@ -18288,8 +19938,13 @@
         </is>
       </c>
       <c r="L280" s="4" t="inlineStr"/>
-      <c r="M280" s="4" t="inlineStr"/>
-      <c r="N280" s="4" t="inlineStr"/>
+      <c r="M280" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr"/>
+      <c r="O280" s="4" t="inlineStr"/>
     </row>
     <row r="281" ht="32" customHeight="1">
       <c r="A281" s="5" t="inlineStr">
@@ -18336,8 +19991,13 @@
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
-      <c r="M281" s="6" t="inlineStr"/>
-      <c r="N281" s="6" t="inlineStr"/>
+      <c r="M281" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" s="6" t="inlineStr"/>
     </row>
     <row r="282" ht="32" customHeight="1">
       <c r="A282" s="3" t="inlineStr">
@@ -18384,8 +20044,13 @@
         </is>
       </c>
       <c r="L282" s="4" t="inlineStr"/>
-      <c r="M282" s="4" t="inlineStr"/>
-      <c r="N282" s="4" t="inlineStr"/>
+      <c r="M282" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" s="4" t="inlineStr"/>
     </row>
     <row r="283" ht="32" customHeight="1">
       <c r="A283" s="5" t="inlineStr">
@@ -18432,8 +20097,13 @@
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
-      <c r="M283" s="6" t="inlineStr"/>
-      <c r="N283" s="6" t="inlineStr"/>
+      <c r="M283" s="6" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr"/>
+      <c r="O283" s="6" t="inlineStr"/>
     </row>
     <row r="284" ht="32" customHeight="1">
       <c r="A284" s="3" t="inlineStr">
@@ -18480,8 +20150,13 @@
         </is>
       </c>
       <c r="L284" s="4" t="inlineStr"/>
-      <c r="M284" s="4" t="inlineStr"/>
-      <c r="N284" s="4" t="inlineStr"/>
+      <c r="M284" s="4" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" s="4" t="inlineStr"/>
     </row>
     <row r="285" ht="32" customHeight="1">
       <c r="A285" s="5" t="inlineStr">
@@ -18528,8 +20203,13 @@
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
-      <c r="M285" s="6" t="inlineStr"/>
-      <c r="N285" s="6" t="inlineStr"/>
+      <c r="M285" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" s="6" t="inlineStr"/>
     </row>
     <row r="286" ht="32" customHeight="1">
       <c r="A286" s="3" t="inlineStr">
@@ -18580,8 +20260,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M286" s="4" t="inlineStr"/>
-      <c r="N286" s="4" t="inlineStr">
+      <c r="M286" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -18636,8 +20321,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M287" s="6" t="inlineStr"/>
-      <c r="N287" s="6" t="inlineStr">
+      <c r="M287" s="6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" s="6" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -18692,8 +20382,13 @@
           <t>83.3</t>
         </is>
       </c>
-      <c r="M288" s="4" t="inlineStr"/>
-      <c r="N288" s="4" t="inlineStr">
+      <c r="M288" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" s="4" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -18744,8 +20439,13 @@
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
-      <c r="M289" s="6" t="inlineStr"/>
-      <c r="N289" s="6" t="inlineStr"/>
+      <c r="M289" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" s="6" t="inlineStr"/>
     </row>
     <row r="290" ht="32" customHeight="1">
       <c r="A290" s="3" t="inlineStr">
@@ -18792,8 +20492,13 @@
         </is>
       </c>
       <c r="L290" s="4" t="inlineStr"/>
-      <c r="M290" s="4" t="inlineStr"/>
-      <c r="N290" s="4" t="inlineStr"/>
+      <c r="M290" s="4" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr"/>
+      <c r="O290" s="4" t="inlineStr"/>
     </row>
     <row r="291" ht="32" customHeight="1">
       <c r="A291" s="5" t="inlineStr">
@@ -18840,8 +20545,13 @@
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
-      <c r="M291" s="6" t="inlineStr"/>
-      <c r="N291" s="6" t="inlineStr"/>
+      <c r="M291" s="6" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr"/>
+      <c r="O291" s="6" t="inlineStr"/>
     </row>
     <row r="292" ht="32" customHeight="1">
       <c r="A292" s="3" t="inlineStr">
@@ -18888,8 +20598,13 @@
         </is>
       </c>
       <c r="L292" s="4" t="inlineStr"/>
-      <c r="M292" s="4" t="inlineStr"/>
-      <c r="N292" s="4" t="inlineStr"/>
+      <c r="M292" s="4" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr"/>
+      <c r="O292" s="4" t="inlineStr"/>
     </row>
     <row r="293" ht="32" customHeight="1">
       <c r="A293" s="5" t="inlineStr">
@@ -18936,8 +20651,13 @@
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
-      <c r="M293" s="6" t="inlineStr"/>
-      <c r="N293" s="6" t="inlineStr"/>
+      <c r="M293" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" s="6" t="inlineStr"/>
     </row>
     <row r="294" ht="32" customHeight="1">
       <c r="A294" s="3" t="inlineStr">
@@ -18984,8 +20704,13 @@
         </is>
       </c>
       <c r="L294" s="4" t="inlineStr"/>
-      <c r="M294" s="4" t="inlineStr"/>
-      <c r="N294" s="4" t="inlineStr"/>
+      <c r="M294" s="4" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr"/>
+      <c r="O294" s="4" t="inlineStr"/>
     </row>
     <row r="295" ht="32" customHeight="1">
       <c r="A295" s="5" t="inlineStr">
@@ -19032,8 +20757,13 @@
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
-      <c r="M295" s="6" t="inlineStr"/>
-      <c r="N295" s="6" t="inlineStr"/>
+      <c r="M295" s="6" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr"/>
+      <c r="O295" s="6" t="inlineStr"/>
     </row>
     <row r="296" ht="32" customHeight="1">
       <c r="A296" s="3" t="inlineStr">
@@ -19080,8 +20810,13 @@
         </is>
       </c>
       <c r="L296" s="4" t="inlineStr"/>
-      <c r="M296" s="4" t="inlineStr"/>
-      <c r="N296" s="4" t="inlineStr"/>
+      <c r="M296" s="4" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" s="4" t="inlineStr"/>
     </row>
     <row r="297" ht="32" customHeight="1">
       <c r="A297" s="5" t="inlineStr">
@@ -19132,8 +20867,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M297" s="6" t="inlineStr"/>
-      <c r="N297" s="6" t="inlineStr">
+      <c r="M297" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr"/>
+      <c r="O297" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -19184,8 +20924,13 @@
         </is>
       </c>
       <c r="L298" s="4" t="inlineStr"/>
-      <c r="M298" s="4" t="inlineStr"/>
-      <c r="N298" s="4" t="inlineStr"/>
+      <c r="M298" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr"/>
+      <c r="O298" s="4" t="inlineStr"/>
     </row>
     <row r="299" ht="32" customHeight="1">
       <c r="A299" s="5" t="inlineStr">
@@ -19232,8 +20977,13 @@
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
-      <c r="M299" s="6" t="inlineStr"/>
-      <c r="N299" s="6" t="inlineStr"/>
+      <c r="M299" s="6" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr"/>
+      <c r="O299" s="6" t="inlineStr"/>
     </row>
     <row r="300" ht="32" customHeight="1">
       <c r="A300" s="3" t="inlineStr">
@@ -19280,8 +21030,13 @@
         </is>
       </c>
       <c r="L300" s="4" t="inlineStr"/>
-      <c r="M300" s="4" t="inlineStr"/>
-      <c r="N300" s="4" t="inlineStr"/>
+      <c r="M300" s="4" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr"/>
+      <c r="O300" s="4" t="inlineStr"/>
     </row>
     <row r="301" ht="32" customHeight="1">
       <c r="A301" s="5" t="inlineStr">
@@ -19328,8 +21083,13 @@
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr"/>
-      <c r="M301" s="6" t="inlineStr"/>
-      <c r="N301" s="6" t="inlineStr"/>
+      <c r="M301" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr"/>
+      <c r="O301" s="6" t="inlineStr"/>
     </row>
     <row r="302" ht="32" customHeight="1">
       <c r="A302" s="3" t="inlineStr">
@@ -19380,8 +21140,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M302" s="4" t="inlineStr"/>
-      <c r="N302" s="4" t="inlineStr">
+      <c r="M302" s="4" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr"/>
+      <c r="O302" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -19432,8 +21197,13 @@
         </is>
       </c>
       <c r="L303" s="6" t="inlineStr"/>
-      <c r="M303" s="6" t="inlineStr"/>
-      <c r="N303" s="6" t="inlineStr"/>
+      <c r="M303" s="6" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr"/>
+      <c r="O303" s="6" t="inlineStr"/>
     </row>
     <row r="304" ht="32" customHeight="1">
       <c r="A304" s="3" t="inlineStr">
@@ -19480,8 +21250,13 @@
         </is>
       </c>
       <c r="L304" s="4" t="inlineStr"/>
-      <c r="M304" s="4" t="inlineStr"/>
-      <c r="N304" s="4" t="inlineStr"/>
+      <c r="M304" s="4" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr"/>
+      <c r="O304" s="4" t="inlineStr"/>
     </row>
     <row r="305" ht="32" customHeight="1">
       <c r="A305" s="5" t="inlineStr">
@@ -19528,8 +21303,13 @@
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
-      <c r="M305" s="6" t="inlineStr"/>
-      <c r="N305" s="6" t="inlineStr"/>
+      <c r="M305" s="6" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr"/>
+      <c r="O305" s="6" t="inlineStr"/>
     </row>
     <row r="306" ht="32" customHeight="1">
       <c r="A306" s="3" t="inlineStr">
@@ -19576,8 +21356,13 @@
         </is>
       </c>
       <c r="L306" s="4" t="inlineStr"/>
-      <c r="M306" s="4" t="inlineStr"/>
-      <c r="N306" s="4" t="inlineStr"/>
+      <c r="M306" s="4" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr"/>
+      <c r="O306" s="4" t="inlineStr"/>
     </row>
     <row r="307" ht="32" customHeight="1">
       <c r="A307" s="5" t="inlineStr">
@@ -19624,8 +21409,13 @@
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
-      <c r="M307" s="6" t="inlineStr"/>
-      <c r="N307" s="6" t="inlineStr"/>
+      <c r="M307" s="6" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr"/>
+      <c r="O307" s="6" t="inlineStr"/>
     </row>
     <row r="308" ht="32" customHeight="1">
       <c r="A308" s="3" t="inlineStr">
@@ -19672,8 +21462,13 @@
         </is>
       </c>
       <c r="L308" s="4" t="inlineStr"/>
-      <c r="M308" s="4" t="inlineStr"/>
-      <c r="N308" s="4" t="inlineStr"/>
+      <c r="M308" s="4" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" s="4" t="inlineStr"/>
     </row>
     <row r="309" ht="32" customHeight="1">
       <c r="A309" s="5" t="inlineStr">
@@ -19720,8 +21515,13 @@
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
-      <c r="M309" s="6" t="inlineStr"/>
-      <c r="N309" s="6" t="inlineStr"/>
+      <c r="M309" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr"/>
+      <c r="O309" s="6" t="inlineStr"/>
     </row>
     <row r="310" ht="32" customHeight="1">
       <c r="A310" s="3" t="inlineStr">
@@ -19768,8 +21568,13 @@
         </is>
       </c>
       <c r="L310" s="4" t="inlineStr"/>
-      <c r="M310" s="4" t="inlineStr"/>
-      <c r="N310" s="4" t="inlineStr"/>
+      <c r="M310" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr"/>
+      <c r="O310" s="4" t="inlineStr"/>
     </row>
     <row r="311" ht="32" customHeight="1">
       <c r="A311" s="5" t="inlineStr">
@@ -19816,8 +21621,13 @@
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
-      <c r="M311" s="6" t="inlineStr"/>
-      <c r="N311" s="6" t="inlineStr"/>
+      <c r="M311" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr"/>
+      <c r="O311" s="6" t="inlineStr"/>
     </row>
     <row r="312" ht="32" customHeight="1">
       <c r="A312" s="3" t="inlineStr">
@@ -19864,8 +21674,13 @@
         </is>
       </c>
       <c r="L312" s="4" t="inlineStr"/>
-      <c r="M312" s="4" t="inlineStr"/>
-      <c r="N312" s="4" t="inlineStr"/>
+      <c r="M312" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr"/>
+      <c r="O312" s="4" t="inlineStr"/>
     </row>
     <row r="313" ht="32" customHeight="1">
       <c r="A313" s="5" t="inlineStr">
@@ -19912,8 +21727,13 @@
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
-      <c r="M313" s="6" t="inlineStr"/>
-      <c r="N313" s="6" t="inlineStr"/>
+      <c r="M313" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr"/>
+      <c r="O313" s="6" t="inlineStr"/>
     </row>
     <row r="314" ht="32" customHeight="1">
       <c r="A314" s="3" t="inlineStr">
@@ -19960,8 +21780,13 @@
         </is>
       </c>
       <c r="L314" s="4" t="inlineStr"/>
-      <c r="M314" s="4" t="inlineStr"/>
-      <c r="N314" s="4" t="inlineStr"/>
+      <c r="M314" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr"/>
+      <c r="O314" s="4" t="inlineStr"/>
     </row>
     <row r="315" ht="32" customHeight="1">
       <c r="A315" s="5" t="inlineStr">
@@ -20008,8 +21833,13 @@
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
-      <c r="M315" s="6" t="inlineStr"/>
-      <c r="N315" s="6" t="inlineStr"/>
+      <c r="M315" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr"/>
+      <c r="O315" s="6" t="inlineStr"/>
     </row>
     <row r="316" ht="32" customHeight="1">
       <c r="A316" s="3" t="inlineStr">
@@ -20056,8 +21886,13 @@
         </is>
       </c>
       <c r="L316" s="4" t="inlineStr"/>
-      <c r="M316" s="4" t="inlineStr"/>
-      <c r="N316" s="4" t="inlineStr"/>
+      <c r="M316" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr"/>
+      <c r="O316" s="4" t="inlineStr"/>
     </row>
     <row r="317" ht="32" customHeight="1">
       <c r="A317" s="5" t="inlineStr">
@@ -20104,8 +21939,13 @@
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr"/>
-      <c r="M317" s="6" t="inlineStr"/>
-      <c r="N317" s="6" t="inlineStr"/>
+      <c r="M317" s="6" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr"/>
+      <c r="O317" s="6" t="inlineStr"/>
     </row>
     <row r="318" ht="32" customHeight="1">
       <c r="A318" s="3" t="inlineStr">
@@ -20152,8 +21992,13 @@
         </is>
       </c>
       <c r="L318" s="4" t="inlineStr"/>
-      <c r="M318" s="4" t="inlineStr"/>
-      <c r="N318" s="4" t="inlineStr"/>
+      <c r="M318" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr"/>
+      <c r="O318" s="4" t="inlineStr"/>
     </row>
     <row r="319" ht="32" customHeight="1">
       <c r="A319" s="5" t="inlineStr">
@@ -20200,8 +22045,13 @@
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr"/>
-      <c r="M319" s="6" t="inlineStr"/>
-      <c r="N319" s="6" t="inlineStr"/>
+      <c r="M319" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr"/>
+      <c r="O319" s="6" t="inlineStr"/>
     </row>
     <row r="320" ht="32" customHeight="1">
       <c r="A320" s="3" t="inlineStr">
@@ -20248,8 +22098,13 @@
         </is>
       </c>
       <c r="L320" s="4" t="inlineStr"/>
-      <c r="M320" s="4" t="inlineStr"/>
-      <c r="N320" s="4" t="inlineStr"/>
+      <c r="M320" s="4" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" s="4" t="inlineStr"/>
     </row>
     <row r="321" ht="32" customHeight="1">
       <c r="A321" s="5" t="inlineStr">
@@ -20300,8 +22155,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M321" s="6" t="inlineStr"/>
-      <c r="N321" s="6" t="inlineStr">
+      <c r="M321" s="6" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr"/>
+      <c r="O321" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -20352,8 +22212,13 @@
         </is>
       </c>
       <c r="L322" s="4" t="inlineStr"/>
-      <c r="M322" s="4" t="inlineStr"/>
-      <c r="N322" s="4" t="inlineStr"/>
+      <c r="M322" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" s="4" t="inlineStr"/>
     </row>
     <row r="323" ht="32" customHeight="1">
       <c r="A323" s="5" t="inlineStr">
@@ -20400,8 +22265,13 @@
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr"/>
-      <c r="M323" s="6" t="inlineStr"/>
-      <c r="N323" s="6" t="inlineStr"/>
+      <c r="M323" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" s="6" t="inlineStr"/>
     </row>
     <row r="324" ht="32" customHeight="1">
       <c r="A324" s="3" t="inlineStr">
@@ -20448,8 +22318,13 @@
         </is>
       </c>
       <c r="L324" s="4" t="inlineStr"/>
-      <c r="M324" s="4" t="inlineStr"/>
-      <c r="N324" s="4" t="inlineStr"/>
+      <c r="M324" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" s="4" t="inlineStr"/>
     </row>
     <row r="325" ht="32" customHeight="1">
       <c r="A325" s="5" t="inlineStr">
@@ -20500,8 +22375,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M325" s="6" t="inlineStr"/>
-      <c r="N325" s="6" t="inlineStr">
+      <c r="M325" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr"/>
+      <c r="O325" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -20552,8 +22432,13 @@
         </is>
       </c>
       <c r="L326" s="4" t="inlineStr"/>
-      <c r="M326" s="4" t="inlineStr"/>
-      <c r="N326" s="4" t="inlineStr"/>
+      <c r="M326" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr"/>
+      <c r="O326" s="4" t="inlineStr"/>
     </row>
     <row r="327" ht="32" customHeight="1">
       <c r="A327" s="5" t="inlineStr">
@@ -20604,8 +22489,13 @@
           <t>50</t>
         </is>
       </c>
-      <c r="M327" s="6" t="inlineStr"/>
-      <c r="N327" s="6" t="inlineStr">
+      <c r="M327" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr"/>
+      <c r="O327" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -20656,8 +22546,13 @@
         </is>
       </c>
       <c r="L328" s="4" t="inlineStr"/>
-      <c r="M328" s="4" t="inlineStr"/>
-      <c r="N328" s="4" t="inlineStr"/>
+      <c r="M328" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr"/>
+      <c r="O328" s="4" t="inlineStr"/>
     </row>
     <row r="329" ht="32" customHeight="1">
       <c r="A329" s="5" t="inlineStr">
@@ -20704,8 +22599,13 @@
         </is>
       </c>
       <c r="L329" s="6" t="inlineStr"/>
-      <c r="M329" s="6" t="inlineStr"/>
-      <c r="N329" s="6" t="inlineStr"/>
+      <c r="M329" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr"/>
+      <c r="O329" s="6" t="inlineStr"/>
     </row>
     <row r="330" ht="32" customHeight="1">
       <c r="A330" s="3" t="inlineStr">
@@ -20756,8 +22656,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M330" s="4" t="inlineStr"/>
-      <c r="N330" s="4" t="inlineStr">
+      <c r="M330" s="4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr"/>
+      <c r="O330" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -20808,8 +22713,13 @@
         </is>
       </c>
       <c r="L331" s="6" t="inlineStr"/>
-      <c r="M331" s="6" t="inlineStr"/>
-      <c r="N331" s="6" t="inlineStr"/>
+      <c r="M331" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr"/>
+      <c r="O331" s="6" t="inlineStr"/>
     </row>
     <row r="332" ht="32" customHeight="1">
       <c r="A332" s="3" t="inlineStr">
@@ -20860,8 +22770,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M332" s="4" t="inlineStr"/>
-      <c r="N332" s="4" t="inlineStr">
+      <c r="M332" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr"/>
+      <c r="O332" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -20912,8 +22827,13 @@
         </is>
       </c>
       <c r="L333" s="6" t="inlineStr"/>
-      <c r="M333" s="6" t="inlineStr"/>
-      <c r="N333" s="6" t="inlineStr"/>
+      <c r="M333" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr"/>
+      <c r="O333" s="6" t="inlineStr"/>
     </row>
     <row r="334" ht="32" customHeight="1">
       <c r="A334" s="3" t="inlineStr">
@@ -20960,8 +22880,13 @@
         </is>
       </c>
       <c r="L334" s="4" t="inlineStr"/>
-      <c r="M334" s="4" t="inlineStr"/>
-      <c r="N334" s="4" t="inlineStr"/>
+      <c r="M334" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr"/>
+      <c r="O334" s="4" t="inlineStr"/>
     </row>
     <row r="335" ht="32" customHeight="1">
       <c r="A335" s="5" t="inlineStr">
@@ -21008,8 +22933,13 @@
         </is>
       </c>
       <c r="L335" s="6" t="inlineStr"/>
-      <c r="M335" s="6" t="inlineStr"/>
-      <c r="N335" s="6" t="inlineStr"/>
+      <c r="M335" s="6" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr"/>
+      <c r="O335" s="6" t="inlineStr"/>
     </row>
     <row r="336" ht="32" customHeight="1">
       <c r="A336" s="3" t="inlineStr">
@@ -21056,8 +22986,13 @@
         </is>
       </c>
       <c r="L336" s="4" t="inlineStr"/>
-      <c r="M336" s="4" t="inlineStr"/>
-      <c r="N336" s="4" t="inlineStr"/>
+      <c r="M336" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr"/>
+      <c r="O336" s="4" t="inlineStr"/>
     </row>
     <row r="337" ht="32" customHeight="1">
       <c r="A337" s="5" t="inlineStr">
@@ -21104,8 +23039,13 @@
         </is>
       </c>
       <c r="L337" s="6" t="inlineStr"/>
-      <c r="M337" s="6" t="inlineStr"/>
-      <c r="N337" s="6" t="inlineStr"/>
+      <c r="M337" s="6" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr"/>
+      <c r="O337" s="6" t="inlineStr"/>
     </row>
     <row r="338" ht="32" customHeight="1">
       <c r="A338" s="3" t="inlineStr">
@@ -21152,8 +23092,13 @@
         </is>
       </c>
       <c r="L338" s="4" t="inlineStr"/>
-      <c r="M338" s="4" t="inlineStr"/>
-      <c r="N338" s="4" t="inlineStr"/>
+      <c r="M338" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr"/>
+      <c r="O338" s="4" t="inlineStr"/>
     </row>
     <row r="339" ht="32" customHeight="1">
       <c r="A339" s="5" t="inlineStr">
@@ -21200,8 +23145,13 @@
         </is>
       </c>
       <c r="L339" s="6" t="inlineStr"/>
-      <c r="M339" s="6" t="inlineStr"/>
-      <c r="N339" s="6" t="inlineStr"/>
+      <c r="M339" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr"/>
+      <c r="O339" s="6" t="inlineStr"/>
     </row>
     <row r="340" ht="32" customHeight="1">
       <c r="A340" s="3" t="inlineStr">
@@ -21248,8 +23198,13 @@
         </is>
       </c>
       <c r="L340" s="4" t="inlineStr"/>
-      <c r="M340" s="4" t="inlineStr"/>
-      <c r="N340" s="4" t="inlineStr"/>
+      <c r="M340" s="4" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr"/>
+      <c r="O340" s="4" t="inlineStr"/>
     </row>
     <row r="341" ht="32" customHeight="1">
       <c r="A341" s="5" t="inlineStr">
@@ -21296,8 +23251,13 @@
         </is>
       </c>
       <c r="L341" s="6" t="inlineStr"/>
-      <c r="M341" s="6" t="inlineStr"/>
-      <c r="N341" s="6" t="inlineStr"/>
+      <c r="M341" s="6" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr"/>
+      <c r="O341" s="6" t="inlineStr"/>
     </row>
     <row r="342" ht="32" customHeight="1">
       <c r="A342" s="3" t="inlineStr">
@@ -21344,8 +23304,13 @@
         </is>
       </c>
       <c r="L342" s="4" t="inlineStr"/>
-      <c r="M342" s="4" t="inlineStr"/>
-      <c r="N342" s="4" t="inlineStr"/>
+      <c r="M342" s="4" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr"/>
+      <c r="O342" s="4" t="inlineStr"/>
     </row>
     <row r="343" ht="32" customHeight="1">
       <c r="A343" s="5" t="inlineStr">
@@ -21396,8 +23361,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M343" s="6" t="inlineStr"/>
-      <c r="N343" s="6" t="inlineStr">
+      <c r="M343" s="6" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr"/>
+      <c r="O343" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -21448,8 +23418,13 @@
         </is>
       </c>
       <c r="L344" s="4" t="inlineStr"/>
-      <c r="M344" s="4" t="inlineStr"/>
-      <c r="N344" s="4" t="inlineStr"/>
+      <c r="M344" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr"/>
+      <c r="O344" s="4" t="inlineStr"/>
     </row>
     <row r="345" ht="32" customHeight="1">
       <c r="A345" s="5" t="inlineStr">
@@ -21500,8 +23475,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M345" s="6" t="inlineStr"/>
-      <c r="N345" s="6" t="inlineStr">
+      <c r="M345" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr"/>
+      <c r="O345" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -21552,8 +23532,13 @@
         </is>
       </c>
       <c r="L346" s="4" t="inlineStr"/>
-      <c r="M346" s="4" t="inlineStr"/>
-      <c r="N346" s="4" t="inlineStr"/>
+      <c r="M346" s="4" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr"/>
+      <c r="O346" s="4" t="inlineStr"/>
     </row>
     <row r="347" ht="32" customHeight="1">
       <c r="A347" s="5" t="inlineStr">
@@ -21604,8 +23589,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M347" s="6" t="inlineStr"/>
-      <c r="N347" s="6" t="inlineStr">
+      <c r="M347" s="6" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr"/>
+      <c r="O347" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -21656,8 +23646,13 @@
         </is>
       </c>
       <c r="L348" s="4" t="inlineStr"/>
-      <c r="M348" s="4" t="inlineStr"/>
-      <c r="N348" s="4" t="inlineStr"/>
+      <c r="M348" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr"/>
+      <c r="O348" s="4" t="inlineStr"/>
     </row>
     <row r="349" ht="32" customHeight="1">
       <c r="A349" s="5" t="inlineStr">
@@ -21705,7 +23700,8 @@
       </c>
       <c r="L349" s="6" t="inlineStr"/>
       <c r="M349" s="6" t="inlineStr"/>
-      <c r="N349" s="6" t="inlineStr"/>
+      <c r="N349" t="inlineStr"/>
+      <c r="O349" s="6" t="inlineStr"/>
     </row>
     <row r="350" ht="32" customHeight="1">
       <c r="A350" s="3" t="inlineStr">
@@ -21753,7 +23749,8 @@
       </c>
       <c r="L350" s="4" t="inlineStr"/>
       <c r="M350" s="4" t="inlineStr"/>
-      <c r="N350" s="4" t="inlineStr"/>
+      <c r="N350" t="inlineStr"/>
+      <c r="O350" s="4" t="inlineStr"/>
     </row>
     <row r="351" ht="32" customHeight="1">
       <c r="A351" s="5" t="inlineStr">
@@ -21800,8 +23797,13 @@
         </is>
       </c>
       <c r="L351" s="6" t="inlineStr"/>
-      <c r="M351" s="6" t="inlineStr"/>
-      <c r="N351" s="6" t="inlineStr"/>
+      <c r="M351" s="6" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr"/>
+      <c r="O351" s="6" t="inlineStr"/>
     </row>
     <row r="352" ht="48" customHeight="1">
       <c r="A352" s="3" t="inlineStr">
@@ -21848,8 +23850,13 @@
         </is>
       </c>
       <c r="L352" s="4" t="inlineStr"/>
-      <c r="M352" s="4" t="inlineStr"/>
-      <c r="N352" s="4" t="inlineStr"/>
+      <c r="M352" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr"/>
+      <c r="O352" s="4" t="inlineStr"/>
     </row>
     <row r="353" ht="48" customHeight="1">
       <c r="A353" s="5" t="inlineStr">
@@ -21900,8 +23907,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M353" s="6" t="inlineStr"/>
-      <c r="N353" s="6" t="inlineStr">
+      <c r="M353" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr"/>
+      <c r="O353" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -21956,8 +23968,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M354" s="4" t="inlineStr"/>
-      <c r="N354" s="4" t="inlineStr">
+      <c r="M354" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr"/>
+      <c r="O354" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -22012,8 +24029,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M355" s="6" t="inlineStr"/>
-      <c r="N355" s="6" t="inlineStr">
+      <c r="M355" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr"/>
+      <c r="O355" s="6" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -22068,8 +24090,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M356" s="4" t="inlineStr"/>
-      <c r="N356" s="4" t="inlineStr">
+      <c r="M356" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr"/>
+      <c r="O356" s="4" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
